--- a/data/trans_bre/P13_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P13_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 3,96</t>
+          <t>-0,42; 3,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,25; 10,42</t>
+          <t>5,01; 10,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 7,29</t>
+          <t>2,01; 7,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 8,96</t>
+          <t>2,17; 8,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 91,31</t>
+          <t>-6,58; 85,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,08; 174,22</t>
+          <t>57,07; 178,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,51; 147,16</t>
+          <t>26,4; 168,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,98; 90,91</t>
+          <t>14,47; 86,98</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,09</t>
+          <t>-0,26; 2,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,05</t>
+          <t>0,91; 3,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,85</t>
+          <t>-0,57; 1,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 2,24</t>
+          <t>-0,75; 2,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 124,42</t>
+          <t>-10,04; 124,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,62; 122,55</t>
+          <t>19,34; 115,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 80,32</t>
+          <t>-17,06; 75,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 79,69</t>
+          <t>-17,58; 80,54</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 4,33</t>
+          <t>-0,17; 4,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 3,36</t>
+          <t>-1,69; 3,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 3,24</t>
+          <t>-1,02; 3,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 0,96</t>
+          <t>-3,01; 0,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 347,5</t>
+          <t>-10,72; 364,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,82; 208,27</t>
+          <t>-47,96; 197,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-39,23; 220,22</t>
+          <t>-33,0; 235,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-53,81; 37,18</t>
+          <t>-57,23; 30,78</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,56</t>
+          <t>0,74; 2,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 5,77</t>
+          <t>3,43; 5,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,17</t>
+          <t>1,07; 3,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,35</t>
+          <t>0,61; 3,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,35; 93,65</t>
+          <t>18,12; 96,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,88; 141,94</t>
+          <t>65,82; 140,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,66; 104,34</t>
+          <t>26,07; 98,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,91; 82,66</t>
+          <t>12,3; 84,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P13_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P13_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>6,41</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 3,71</t>
+          <t>-0,15; 3,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,01; 10,53</t>
+          <t>5,23; 10,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 7,73</t>
+          <t>2,19; 7,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 8,99</t>
+          <t>3,17; 9,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 85,21</t>
+          <t>-3,1; 90,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,07; 178,01</t>
+          <t>59,36; 181,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,4; 168,42</t>
+          <t>29,09; 148,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,47; 86,98</t>
+          <t>23,3; 97,97</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 2,15</t>
+          <t>-0,27; 2,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,83</t>
+          <t>0,93; 3,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,79</t>
+          <t>-0,49; 1,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,27</t>
+          <t>-0,37; 2,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 124,6</t>
+          <t>-9,84; 128,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,34; 115,91</t>
+          <t>19,67; 119,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 75,65</t>
+          <t>-14,59; 78,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 80,54</t>
+          <t>-8,05; 61,25</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,93</t>
+          <t>-0,68</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-24,28%</t>
+          <t>-18,07%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,2</t>
+          <t>-0,04; 4,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 3,49</t>
+          <t>-1,52; 3,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 3,42</t>
+          <t>-1,02; 3,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,73</t>
+          <t>-2,55; 0,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 364,29</t>
+          <t>-8,59; 343,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,96; 197,88</t>
+          <t>-41,69; 216,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,0; 235,06</t>
+          <t>-34,02; 217,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-57,23; 30,78</t>
+          <t>-51,07; 37,17</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>2,22</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>42,45%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,69</t>
+          <t>0,58; 2,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,84</t>
+          <t>3,37; 5,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,01</t>
+          <t>0,96; 3,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,27</t>
+          <t>1,16; 3,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,12; 96,14</t>
+          <t>15,73; 94,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,82; 140,66</t>
+          <t>64,16; 139,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,07; 98,25</t>
+          <t>23,83; 99,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,3; 84,04</t>
+          <t>20,37; 68,08</t>
         </is>
       </c>
     </row>
